--- a/public/metacube/thruster/data/propellant_selection.xlsx
+++ b/public/metacube/thruster/data/propellant_selection.xlsx
@@ -30,7 +30,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -40,6 +40,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00DDE5F0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF3C4"/>
       </patternFill>
     </fill>
   </fills>
@@ -55,11 +60,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -456,7 +462,7 @@
     <col width="9" customWidth="1" min="22" max="22"/>
     <col width="9" customWidth="1" min="23" max="23"/>
     <col width="8" customWidth="1" min="24" max="24"/>
-    <col width="14" customWidth="1" min="25" max="25"/>
+    <col width="16" customWidth="1" min="25" max="25"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -861,7 +867,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>선택</t>
+          <t>1차 후보(참고)</t>
         </is>
       </c>
     </row>
@@ -955,95 +961,95 @@
       <c r="Y5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>R1233zd(E)</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>R1233zd(E)</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>102687-65-0</t>
         </is>
       </c>
-      <c r="D6" t="n">
+      <c r="D6" s="2" t="n">
         <v>130.5</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6" s="2" t="n">
         <v>18.3</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F6" s="2" t="n">
         <v>166.5</v>
       </c>
-      <c r="G6" t="n">
+      <c r="G6" s="2" t="n">
         <v>1.08</v>
       </c>
-      <c r="H6" t="n">
+      <c r="H6" s="2" t="n">
         <v>4.48</v>
       </c>
-      <c r="I6" t="n">
+      <c r="I6" s="2" t="n">
         <v>1275</v>
       </c>
-      <c r="J6" t="n">
+      <c r="J6" s="2" t="n">
         <v>60.8</v>
       </c>
-      <c r="K6" t="n">
+      <c r="K6" s="2" t="n">
         <v>70.8</v>
       </c>
-      <c r="L6" t="n">
+      <c r="L6" s="2" t="n">
         <v>1.1</v>
       </c>
-      <c r="M6" t="n">
+      <c r="M6" s="2" t="n">
         <v>44.8</v>
       </c>
-      <c r="N6" t="n">
+      <c r="N6" s="2" t="n">
         <v>57.2</v>
       </c>
-      <c r="O6" t="n">
+      <c r="O6" s="2" t="n">
         <v>231</v>
       </c>
-      <c r="P6" t="n">
+      <c r="P6" s="2" t="n">
         <v>0.525</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="Q6" s="2" t="n">
         <v>26.3</v>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="R6" s="2" t="inlineStr">
         <is>
           <t>A1</t>
         </is>
       </c>
-      <c r="S6" t="n">
+      <c r="S6" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="T6" s="2" t="inlineStr"/>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="W6" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="X6" s="2" t="inlineStr">
         <is>
           <t>★</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>HFO</t>
+      <c r="Y6" s="2" t="inlineStr">
+        <is>
+          <t>선택</t>
         </is>
       </c>
     </row>
@@ -5136,324 +5142,346 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
     <col width="80" customWidth="1" min="2" max="2"/>
     <col width="80" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>정의 / 계산식</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>출처 / 근거</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>비고</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>선정 추진제 (2026-08-17 변경)</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>R1233zd(E) — trans-1-chloro-3,3,3-trifluoropropene (HFO), CAS 102687-65-0. 무독·불연(ASHRAE A1)·GWP 1. 설계점: T_sat(4 bar) 60.8 °C, ṁ 113.7 mg/s(5.35 mL/min), 요구 전력 26.0 W, Isp 44.8 s. 하드웨어(채널·히터·노즐 φ0.30·리스트릭터 φ0.15) 변경 없음</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>본 설계 결정 — R245fa(B1, GWP 858)는 1차 후보(참고)로 유지</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>상관식 DB(Kim-Mudawar·Bertsch)에 R1233zd(E) 미포함 — 밴드 접근 유지, 실측이 신규 데이터</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>열역학 물성 전체(P_sat, ρ, h, cp, cv, M, Tcrit, CAS)</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>CoolProp 7.2.0 PropsSI (각 유체의 헬름홀츠 자유에너지 기준 상태방정식; R245fa=Akasaka 2015 등 — 유체별 EOS 참고문헌은 CoolProp 문서/`get_fluid_param_string(fluid,"BibTeX-EOS")`)</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>Bell, Wronski, Quoilin, Lemort, "Pure and Pseudo-pure Fluid Thermophysical Property Evaluation and the Open-Source Thermophysical Property Library CoolProp", Ind. Eng. Chem. Res. 53(6), 2498–2508 (2014), doi:10.1021/ie4033999 — http://www.coolprop.org</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>CoolProp 7.2.0 PropsSI (유체별 헬름홀츠 EOS; R1233zd(E)=Mondejar-McLinden 2015 계열 — CoolProp 문서 참조)</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>Bell et al., Ind. Eng. Chem. Res. 53(6), 2498–2508 (2014), doi:10.1021/ie4033999 — http://www.coolprop.org</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>NIST REFPROP급 EOS</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>저장압 P_sat(20 °C)</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>20 °C 포화증기압. 시린지펌프·박판 저압탱크 조건 ≤1.5 bar (창 1)</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>CoolProp; 기준 1.5 bar = 본 설계 판단(시린지펌프 배압·FR-4/얇은 탱크 허용)</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>가스(Tcrit&lt;20 °C)는 200 bar 탱크로 가정</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>CoolProp; 기준 1.5 bar = 본 설계 판단</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>가스(Tcrit&lt;20 °C)는 200 bar 탱크 가정</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>P_sat(65 °C) = MEOP@65 °C</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>PCB(FR-4·솔더) 온도 한계 65 °C에서 도달 가능한 최대 챔버 압력 = 65 °C 저장 시 탱크 MEOP. 창 2: ≥3 bar (유용한 노즐 압력비)</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>CoolProp; 65 °C 한계·3 bar 기준 = 본 설계 판단</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>Tcrit&lt;65 °C면 초임계(상한 없음)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>PCB 온도 한계 65 °C에서 도달 가능한 최대 챔버 압력 = 65 °C 저장 시 탱크 MEOP. 창 2: ≥3 bar</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>CoolProp; 65 °C·3 bar 기준 = 본 설계 판단</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>R1233zd(E) 4.48 bar — 챔버 4.0 bar 위 여유 0.48</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>ρ 액체 20 °C</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>20 °C 포화액 밀도. 가스는 200 bar·20 °C 밀도</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>CoolProp</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="D6" s="4" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>T_sat 4 bar, T0</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>챔버 4.0 bar abs 포화온도, T0 = T_sat + 10 K(과열). 가스는 20 °C</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>CoolProp; 4 bar·10 K = 본 설계점</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>R245fa: 55.0 / 65.0 °C</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>CoolProp; 설계점</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>R1233zd(E): 60.8 / 70.8 °C</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>γ</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>증기 cp/cv at T0, 2 bar(또는 0.3 Pcrit 중 작은 값)</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>CoolProp</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="D8" s="4" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>Isp 진공</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Isp = η·uₑ/g₀, uₑ = √(2γ/(γ−1)·R·T0/M·[1−(Pₑ/P₀)^((γ−1)/γ)]), 면적비 ε=100에서 Mₑ 역산(등엔트로피 면적-마하 관계), 압력추력항 생략, η=0.93</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>Sutton &amp; Biblarz, Rocket Propulsion Elements (9th ed.), Ch.3 이상노즐식; η 0.93 = 마이크로노즐 문헌 범위(0.85–0.95) 가정</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>이상기체 가정 — 실기체(Z 0.90–0.93) 시 C* 3–5 % 차</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Isp = η·uₑ/g₀, uₑ = √(2γ/(γ−1)·R·T0/M·[1−(Pₑ/P₀)^((γ−1)/γ)]), ε=100 Mₑ 역산, 압력추력항 생략, η=0.93</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>Sutton &amp; Biblarz, Rocket Propulsion Elements (9th ed.), Ch.3; η 0.93 = 마이크로노즐 문헌 범위 가정</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>실기체 Z 0.90 시 C* 3–5 % 차</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>ρ·Isp</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>밀도-비추력 = ρ(20 °C) × Isp / 1000 [g·s/cm³]</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>정의</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="D10" s="4" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>Δh, W/mN, 50 mN 전력</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>Δh = h(4 bar, T0 증기) − h(20 °C 액체); W/mN = Δh/(Isp·g₀)/1000; 50 mN 전력 = 50 × W/mN (히터 손실 제외)</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>CoolProp 엔탈피; 정의</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>R245fa 0.53 W/mN</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>R1233zd(E) 0.53 W/mN</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>ASHRAE 34 안전등급</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>A/B = 저/고 독성(OEL 400 ppm 기준), 1/2L/2/3 = 불연/저가연/가연/고가연</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>ANSI/ASHRAE Standard 34-2022 "Designation and Safety Classification of Refrigerants" (냉매); 비냉매(용매·탄화수소·가스)는 등가 판단 표기</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>R245fa = B1(허니웰 SDS·ASHRAE 34)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>ANSI/ASHRAE Standard 34-2022; 비냉매는 등가 판단 표기</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>R1233zd(E) = A1(무독·불연)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>GWP (100년)</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>지구온난화지수</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>IPCC AR5(2013)/AR6(2021) 부속표 및 제조사 자료 기반 문헌값 — 투고 전 원출처(IPCC 표) 재확인 필요</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>R245fa 858(AR5) / R1233zd(E) 1 / R1234ze(Z) &lt;1</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>IPCC AR5/AR6 부속표 및 제조사 자료 기반 문헌값 — 투고 전 원출처 재확인</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>R1233zd(E) 1 / R245fa 858</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>창(feasibility) 판정</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>창1 저장압≤1.5 bar AND 창2 MEOP(65 °C)≥3 bar AND 창3 불연(1급 또는 A2L) → ★</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>본 설계 요구(시린지펌프 급송·PCB 온도 한계·실험실 안전)</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>5종: R11·R123·R245fa·R1234ze(Z)·R1233zd(E) → 규제 제외 시 3종</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>본 설계 요구</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>5종: R11·R123·R245fa·R1234ze(Z)·R1233zd(E) → 규제 제외 3종</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>제외 유체</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>R1336mzz(Z), R1224yd(Z)는 CoolProp 미지원으로 미계산(문헌: A1, GWP≤2, Tb 33/14 °C — 창 안 후보 가능)</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>R1336mzz(Z)·R1224yd(Z)는 CoolProp 미지원(문헌상 A1, GWP≤2 — 창 안 후보 가능)</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D14" s="3" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="D15" s="4" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>생성</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>design/propellant_selection.py · propellant_selection.json · 생성일 2026-08-16</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>design/propellant_selection.py · propellant_selection.json · 생성일 2026-08-24</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
         <is>
           <t>coldgas-thruster 리포지토리</t>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr"/>
+      <c r="D16" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
